--- a/web/public/forms/orig/o-bangsu-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-bangsu-gyehoekseo.xlsx
@@ -855,7 +855,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="58" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2855,7 +2855,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5120,7 +5120,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7297,7 +7297,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="58" t="inlineStr">
@@ -7394,7 +7394,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="58" t="inlineStr">
@@ -8727,7 +8727,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="58" t="inlineStr">
@@ -10993,7 +10993,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="N1" s="58" t="inlineStr">

--- a/web/public/forms/orig/o-bangsu-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-bangsu-gyehoekseo.xlsx
@@ -826,7 +826,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4266,7 +4266,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
